--- a/data_processed/results_OLS_m3_gas_per_capitatenure.xlsx
+++ b/data_processed/results_OLS_m3_gas_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.7289" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.7291" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1418.849664153037</v>
+        <v>1421.685019396884</v>
       </c>
       <c r="D2" t="n">
-        <v>1.375570132813607e-93</v>
+        <v>6.455494369824731e-95</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-57.67568960929002</v>
+        <v>-57.94613602308021</v>
       </c>
       <c r="D3" t="n">
-        <v>3.357390225139065e-18</v>
+        <v>4.000255779991708e-19</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-152.2527752320114</v>
+        <v>-422.7249529087079</v>
       </c>
       <c r="D4" t="n">
-        <v>1.851491934232331e-151</v>
+        <v>7.677554358387805e-284</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.95056371301818</v>
+        <v>5.971216365877424</v>
       </c>
       <c r="D5" t="n">
-        <v>8.995719691110546e-28</v>
+        <v>4.747753088884677e-40</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.45944664268433</v>
+        <v>-152.3402167190769</v>
       </c>
       <c r="D6" t="n">
-        <v>3.698577750803771e-12</v>
+        <v>2.770886466949837e-152</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-422.3351354473213</v>
+        <v>32.86389289716724</v>
       </c>
       <c r="D7" t="n">
-        <v>7.600236013632602e-284</v>
+        <v>2.208004209133211e-27</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.989511245709768</v>
+        <v>23.51766157913674</v>
       </c>
       <c r="D8" t="n">
-        <v>2.127449527115539e-44</v>
+        <v>8.272784758118758e-13</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-568.8019203975547</v>
+        <v>-569.5874486034691</v>
       </c>
       <c r="D9" t="n">
-        <v>3.680834484712223e-22</v>
+        <v>3.247624537971731e-22</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-664.7556713941256</v>
+        <v>-665.1852477788069</v>
       </c>
       <c r="D10" t="n">
-        <v>3.430393365270293e-23</v>
+        <v>1.744299554091246e-22</v>
       </c>
     </row>
   </sheetData>
